--- a/data/trans_bre/IP19C01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 28,92</t>
+          <t>-14,76; 27,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 32,14</t>
+          <t>-12,03; 31,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 10,66</t>
+          <t>-31,69; 10,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 50,61</t>
+          <t>-18,95; 49,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 74,19</t>
+          <t>-18,25; 70,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 20,24</t>
+          <t>-42,44; 19,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 8,61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 12,4</t>
+          <t>-12,5; 15,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 13,99</t>
+          <t>-10,18; 14,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 19,36</t>
+          <t>-11,58; 17,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 14,05</t>
+          <t>-17,72; 15,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 18,5</t>
+          <t>-15,68; 21,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 18,87</t>
+          <t>-12,17; 19,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 31,24</t>
+          <t>-15,07; 27,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 24,47</t>
+          <t>-23,61; 26,39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,0; -3,27</t>
+          <t>-40,22; -4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 7,23</t>
+          <t>-17,37; 7,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 7,76</t>
+          <t>-21,46; 8,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 10,83</t>
+          <t>-20,46; 9,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -4,56</t>
+          <t>-50,22; -4,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 8,55</t>
+          <t>-18,72; 8,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 9,33</t>
+          <t>-23,14; 10,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 14,3</t>
+          <t>-22,98; 13,02</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,42; -1,2</t>
+          <t>-33,44; -3,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 7,42</t>
+          <t>-25,34; 8,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,56; -3,1</t>
+          <t>-34,02; -2,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 12,45</t>
+          <t>-28,65; 10,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,93; -1,51</t>
+          <t>-40,41; -4,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 10,41</t>
+          <t>-31,36; 12,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,5; -4,97</t>
+          <t>-42,77; -3,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 18,55</t>
+          <t>-34,96; 16,43</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 14,66</t>
+          <t>-29,52; 15,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 11,82</t>
+          <t>-18,86; 12,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 21,57</t>
+          <t>-25,85; 20,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 7,45</t>
+          <t>-3,37; 8,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 23,98</t>
+          <t>-37,68; 27,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 14,69</t>
+          <t>-20,13; 15,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 32,05</t>
+          <t>-28,96; 31,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 8,35</t>
+          <t>-3,37; 9,68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 11,8</t>
+          <t>-29,46; 11,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 14,57</t>
+          <t>-17,45; 12,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 11,96</t>
+          <t>-16,45; 11,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,15; 32,37</t>
+          <t>3,38; 32,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 21,27</t>
+          <t>-40,21; 20,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 20,2</t>
+          <t>-19,98; 16,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 15,38</t>
+          <t>-18,43; 15,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 50,19</t>
+          <t>3,93; 50,17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 13,01</t>
+          <t>-12,07; 14,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 6,26</t>
+          <t>-19,99; 5,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 9,32</t>
+          <t>-10,21; 9,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 7,98</t>
+          <t>-14,38; 7,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 21,76</t>
+          <t>-16,22; 24,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 8,79</t>
+          <t>-24,0; 7,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 11,47</t>
+          <t>-11,22; 11,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 11,21</t>
+          <t>-17,83; 11,02</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 10,78</t>
+          <t>-14,14; 11,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 5,95</t>
+          <t>-20,15; 6,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 15,9</t>
+          <t>-6,43; 16,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 8,31</t>
+          <t>-4,21; 9,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 17,31</t>
+          <t>-18,74; 17,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 9,9</t>
+          <t>-28,04; 11,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 26,37</t>
+          <t>-8,63; 27,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 9,57</t>
+          <t>-4,3; 10,67</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 0,12</t>
+          <t>-11,19; 0,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,63</t>
+          <t>-9,38; 0,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 2,89</t>
+          <t>-7,32; 3,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,52</t>
+          <t>-5,38; 4,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 0,12</t>
+          <t>-15,04; 0,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,29</t>
+          <t>-11,88; 1,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 3,96</t>
+          <t>-9,33; 4,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,69</t>
+          <t>-6,28; 5,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 27,92</t>
+          <t>-13,4; 29,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 31,81</t>
+          <t>-10,2; 33,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 10,57</t>
+          <t>-30,31; 11,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 8,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 49,34</t>
+          <t>-16,75; 52,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 70,83</t>
+          <t>-16,13; 78,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 19,43</t>
+          <t>-41,95; 21,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 9,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 15,1</t>
+          <t>-10,08; 14,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 14,43</t>
+          <t>-11,39; 13,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 17,29</t>
+          <t>-10,27; 17,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 15,47</t>
+          <t>-18,52; 13,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 21,84</t>
+          <t>-12,39; 21,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 19,88</t>
+          <t>-13,52; 19,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 27,82</t>
+          <t>-13,9; 28,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 26,39</t>
+          <t>-25,66; 23,44</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-40,22; -4,0</t>
+          <t>-39,26; -2,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 7,17</t>
+          <t>-17,37; 8,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 8,34</t>
+          <t>-20,04; 9,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 9,93</t>
+          <t>-21,55; 8,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,22; -4,32</t>
+          <t>-51,62; -4,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 8,52</t>
+          <t>-18,41; 9,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 10,35</t>
+          <t>-21,95; 11,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 13,02</t>
+          <t>-24,19; 11,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,44; -3,06</t>
+          <t>-36,19; -2,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 8,37</t>
+          <t>-25,94; 7,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,02; -2,37</t>
+          <t>-33,47; -2,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 10,54</t>
+          <t>-28,52; 14,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,41; -4,22</t>
+          <t>-40,23; -3,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 12,49</t>
+          <t>-32,03; 10,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,77; -3,56</t>
+          <t>-42,18; -3,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 16,43</t>
+          <t>-33,93; 22,75</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 15,32</t>
+          <t>-29,32; 12,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 12,33</t>
+          <t>-20,81; 12,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 20,87</t>
+          <t>-27,75; 21,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 8,66</t>
+          <t>-3,48; 8,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 27,04</t>
+          <t>-37,52; 22,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 15,07</t>
+          <t>-22,31; 16,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 31,08</t>
+          <t>-32,12; 31,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 9,68</t>
+          <t>-3,48; 9,24</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 11,26</t>
+          <t>-32,28; 11,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 12,39</t>
+          <t>-18,12; 12,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 11,97</t>
+          <t>-15,59; 11,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,38; 32,02</t>
+          <t>3,26; 31,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,21; 20,59</t>
+          <t>-41,43; 21,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 16,42</t>
+          <t>-21,37; 17,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 15,98</t>
+          <t>-17,65; 15,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 50,17</t>
+          <t>3,96; 49,91</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 14,63</t>
+          <t>-12,48; 14,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 5,51</t>
+          <t>-21,21; 5,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 9,37</t>
+          <t>-9,32; 10,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 7,61</t>
+          <t>-16,0; 7,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 24,4</t>
+          <t>-16,71; 24,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 7,29</t>
+          <t>-24,44; 7,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 11,63</t>
+          <t>-10,28; 12,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 11,02</t>
+          <t>-19,85; 11,02</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 11,22</t>
+          <t>-12,54; 9,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 6,36</t>
+          <t>-19,82; 6,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 16,63</t>
+          <t>-6,83; 16,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 9,31</t>
+          <t>-4,29; 8,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 17,49</t>
+          <t>-16,79; 15,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 11,17</t>
+          <t>-28,03; 10,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 27,63</t>
+          <t>-9,62; 27,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 10,67</t>
+          <t>-4,49; 8,98</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 0,11</t>
+          <t>-10,88; -0,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,99</t>
+          <t>-9,08; 1,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,1</t>
+          <t>-7,85; 2,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,11</t>
+          <t>-5,83; 3,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 0,17</t>
+          <t>-14,73; -0,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 1,32</t>
+          <t>-11,64; 2,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,2</t>
+          <t>-9,8; 3,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,12</t>
+          <t>-7,0; 4,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 29,77</t>
+          <t>-15,11; 28,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 33,86</t>
+          <t>-8,4; 32,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 11,32</t>
+          <t>-28,99; 10,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,63</t>
+          <t>0,0; 9,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 52,7</t>
+          <t>-19,45; 50,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 78,43</t>
+          <t>-13,42; 74,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,95; 21,16</t>
+          <t>-41,33; 20,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,45</t>
+          <t>0,0; 10,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-3,26%</t>
+          <t>-0,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 14,34</t>
+          <t>-11,48; 12,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 13,81</t>
+          <t>-11,27; 13,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 17,87</t>
+          <t>-10,19; 19,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 13,69</t>
+          <t>-16,04; 15,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 21,35</t>
+          <t>-14,22; 18,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 19,46</t>
+          <t>-13,41; 18,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 28,64</t>
+          <t>-12,9; 31,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 23,44</t>
+          <t>-21,77; 27,81</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-6,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-6,47%</t>
+          <t>-7,33%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,26; -2,41</t>
+          <t>-41,0; -3,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 8,17</t>
+          <t>-17,73; 7,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 9,32</t>
+          <t>-21,43; 7,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 8,98</t>
+          <t>-20,11; 9,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,62; -4,93</t>
+          <t>-52,72; -4,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 9,45</t>
+          <t>-18,95; 8,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 11,46</t>
+          <t>-23,2; 9,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 11,34</t>
+          <t>-22,29; 12,16</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,08</t>
+          <t>-7,33</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,02%</t>
+          <t>-9,94%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,19; -2,85</t>
+          <t>-33,42; -1,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 7,17</t>
+          <t>-25,78; 7,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,47; -2,2</t>
+          <t>-33,56; -3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 14,76</t>
+          <t>-27,01; 14,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,23; -3,29</t>
+          <t>-38,93; -1,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 10,44</t>
+          <t>-31,93; 10,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,18; -3,62</t>
+          <t>-42,5; -4,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 22,75</t>
+          <t>-32,11; 23,14</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 12,92</t>
+          <t>-30,34; 14,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 12,75</t>
+          <t>-19,53; 11,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 21,96</t>
+          <t>-24,36; 21,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 8,4</t>
+          <t>-3,93; 6,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,52; 22,29</t>
+          <t>-38,32; 23,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 16,42</t>
+          <t>-20,66; 14,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 31,46</t>
+          <t>-28,59; 32,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 9,24</t>
+          <t>-3,98; 7,55</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,22</t>
+          <t>15,38</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 11,39</t>
+          <t>-30,52; 11,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 12,27</t>
+          <t>-19,33; 14,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 11,72</t>
+          <t>-19,06; 11,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 31,48</t>
+          <t>2,68; 30,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 21,61</t>
+          <t>-41,7; 21,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 17,23</t>
+          <t>-21,72; 20,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 15,49</t>
+          <t>-21,36; 15,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 49,91</t>
+          <t>3,36; 47,61</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-4,73</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-4,06%</t>
+          <t>-6,13%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 14,35</t>
+          <t>-13,1; 13,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 5,56</t>
+          <t>-18,96; 6,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 10,02</t>
+          <t>-10,07; 9,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 7,94</t>
+          <t>-15,97; 7,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 24,6</t>
+          <t>-17,37; 21,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 7,74</t>
+          <t>-21,86; 8,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 12,3</t>
+          <t>-11,07; 11,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 11,02</t>
+          <t>-19,63; 10,24</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 9,67</t>
+          <t>-12,63; 10,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 6,46</t>
+          <t>-19,03; 5,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 16,22</t>
+          <t>-6,93; 15,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 8,06</t>
+          <t>-3,3; 8,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 15,35</t>
+          <t>-16,91; 17,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 10,66</t>
+          <t>-27,66; 9,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 27,09</t>
+          <t>-9,39; 26,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 8,98</t>
+          <t>-3,44; 9,84</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-0,9%</t>
+          <t>-0,84%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,03</t>
+          <t>-10,68; 0,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,67</t>
+          <t>-8,99; 1,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,65</t>
+          <t>-7,57; 2,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,9</t>
+          <t>-5,21; 4,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -0,15</t>
+          <t>-14,6; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 2,24</t>
+          <t>-11,43; 2,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 3,68</t>
+          <t>-9,64; 3,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,86</t>
+          <t>-6,15; 5,87</t>
         </is>
       </c>
     </row>
